--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="172">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -385,7 +385,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use</t>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
   </si>
   <si>
     <t>XPN.7, but often indicated by which field contains the name</t>
@@ -1519,9 +1522,11 @@
       <c r="X6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y6" s="2"/>
+      <c r="Y6" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="Z6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1554,21 +1559,21 @@
         <v>85</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1594,16 +1599,16 @@
         <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>77</v>
@@ -1652,7 +1657,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1667,10 +1672,10 @@
         <v>85</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1678,14 +1683,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1707,13 +1712,13 @@
         <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1763,7 +1768,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -1778,25 +1783,25 @@
         <v>85</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1818,13 +1823,13 @@
         <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1874,7 +1879,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1889,21 +1894,21 @@
         <v>85</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1929,10 +1934,10 @@
         <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1959,13 +1964,13 @@
         <v>77</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>77</v>
@@ -1983,7 +1988,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1998,21 +2003,21 @@
         <v>85</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2038,10 +2043,10 @@
         <v>91</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2068,13 +2073,13 @@
         <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>77</v>
@@ -2092,7 +2097,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2107,10 +2112,10 @@
         <v>85</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2144,17 +2149,17 @@
         <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2203,7 +2208,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2218,13 +2223,13 @@
         <v>85</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile of datatype HumanName with constraints on prefix and suffix | Profilage du type de données HumanName pour prise en compte de la civilté au niveau de l'élément prefix et du titre au niveau de l'élément suffix</t>
+    <t>Profilage du type de données HumanName pour prise en compte de la civilté au niveau de l'élément prefix et du titre au niveau de l'élément suffix
+.French profile of datatype HumanName with constraints on prefix and suffix</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,7 +351,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
 </t>
   </si>
   <si>
@@ -865,7 +865,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="33.8671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="38.39453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="170">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -484,7 +484,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques du RASS</t>
+    <t>Civilités des personnes physiques</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
@@ -502,16 +502,10 @@
     <t>HumanName.suffix</t>
   </si>
   <si>
-    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+    <t>Parts that come after the name</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>Civilités d'exercice d'un professionnel du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
   </si>
   <si>
     <t>XPN/4</t>
@@ -879,8 +873,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="37.77734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.34765625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="27.484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2074,13 +2068,13 @@
         <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>77</v>
@@ -2113,10 +2107,10 @@
         <v>85</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2124,10 +2118,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2150,17 +2144,17 @@
         <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2209,7 +2203,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2224,13 +2218,13 @@
         <v>85</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,7 +351,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>Civilités des personnes physiques</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
   </si>
   <si>
     <t>XPN.5</t>
@@ -859,7 +859,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="38.39453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="46.421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -874,7 +874,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="27.484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.01171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.7265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
